--- a/Assets/06 Data/ExcelData/dt_etc_item.xlsx
+++ b/Assets/06 Data/ExcelData/dt_etc_item.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\StudyUnity\Duckov\Assets\06 Data\ExcelData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Genie\Desktop\duckov-clone\Assets\06 Data\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E14D89F-59B9-4117-93BE-A363F65FCACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68D9AED-B7F3-4706-B040-E40031DAAFA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE0583BB-D93F-48B9-9871-CCD056A6EF96}"/>
+    <workbookView xWindow="6750" yWindow="2775" windowWidth="20595" windowHeight="11295" xr2:uid="{EE0583BB-D93F-48B9-9871-CCD056A6EF96}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -86,10 +86,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>uint</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>string</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -155,6 +151,10 @@
   </si>
   <si>
     <t>Rarity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -618,7 +618,7 @@
         <v>7</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>8</v>
@@ -633,62 +633,62 @@
         <v>11</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="H2" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>14</v>
-      </c>
       <c r="G3" s="4" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -696,7 +696,7 @@
         <v>361</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>0</v>
@@ -722,7 +722,7 @@
         <v>362</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>0</v>
@@ -748,7 +748,7 @@
         <v>76</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>0</v>
@@ -774,7 +774,7 @@
         <v>111</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>0</v>
@@ -800,7 +800,7 @@
         <v>1241</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>0</v>
@@ -826,7 +826,7 @@
         <v>328</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>0</v>

--- a/Assets/06 Data/ExcelData/dt_etc_item.xlsx
+++ b/Assets/06 Data/ExcelData/dt_etc_item.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Genie\Desktop\duckov-clone\Assets\06 Data\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68D9AED-B7F3-4706-B040-E40031DAAFA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B77A0E63-3154-4D0D-83FD-BB3F515A99D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6750" yWindow="2775" windowWidth="20595" windowHeight="11295" xr2:uid="{EE0583BB-D93F-48B9-9871-CCD056A6EF96}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,87 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="41">
+  <si>
+    <t>//번호</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>등급</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>분류</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가치</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>무게</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가중치</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 소지 스택</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rarity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weight</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeightValue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStackSize</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
   <si>
     <t>Etc</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -50,7 +130,41 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>R6 배터리</t>
+  </si>
+  <si>
+    <t>로프</t>
+  </si>
+  <si>
+    <t>신문</t>
+  </si>
+  <si>
+    <t>무기 부품</t>
+  </si>
+  <si>
+    <t>조약돌</t>
+  </si>
+  <si>
+    <t>고급</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>축구공</t>
+  </si>
+  <si>
+    <t>고급</t>
+  </si>
+  <si>
+    <t>타이어</t>
+  </si>
+  <si>
+    <t>노트</t>
+  </si>
+  <si>
+    <t>주사위</t>
+  </si>
+  <si>
+    <t>희귀</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -58,103 +172,21 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>금속 통</t>
+  </si>
+  <si>
+    <t>트럼펫</t>
+  </si>
+  <si>
+    <t>전설</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>자동차 배터리</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>그래픽카드</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>//번호</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>분류</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>가치</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>무게</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>float</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>가중치</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Value</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Weight</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>WeightValue</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>등급</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>일반</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>고급</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>희귀</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>전설</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대 소지 스택</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStackSize</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rarity</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -162,7 +194,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -600,8 +632,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14B1B0CD-82CA-4F60-9855-B60A8FBED752}">
-  <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H57"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="6.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.75" customWidth="1"/>
@@ -613,96 +645,96 @@
     <col min="8" max="8" width="12.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="E2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>13</v>
-      </c>
       <c r="G3" s="4" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>361</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E4" s="1">
         <v>102</v>
@@ -717,18 +749,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>362</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>2</v>
       </c>
       <c r="E5" s="1">
         <v>178</v>
@@ -743,124 +775,702 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="E6" s="1">
-        <v>845</v>
+        <v>200</v>
       </c>
       <c r="F6" s="1">
-        <v>0.51</v>
+        <v>0.08</v>
       </c>
       <c r="G6" s="1">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H6" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="E7" s="1">
-        <v>2837</v>
+        <v>255</v>
       </c>
       <c r="F7" s="1">
-        <v>2.0299999999999998</v>
+        <v>1.03</v>
       </c>
       <c r="G7" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H7" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
-        <v>1241</v>
+        <v>116</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="E8" s="1">
-        <v>7515</v>
+        <v>347</v>
       </c>
       <c r="F8" s="1">
-        <v>18.46</v>
+        <v>0.25</v>
       </c>
       <c r="G8" s="1">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H8" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
+        <v>367</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="1">
+        <v>449</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.38</v>
+      </c>
+      <c r="G9" s="1">
+        <v>16</v>
+      </c>
+      <c r="H9" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1">
+        <v>932</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="1">
+        <v>40</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>15</v>
+      </c>
+      <c r="H10" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1">
+        <v>76</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="1">
+        <v>484</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.51</v>
+      </c>
+      <c r="G11" s="1">
+        <v>10</v>
+      </c>
+      <c r="H11" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1">
+        <v>127</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="1">
+        <v>845</v>
+      </c>
+      <c r="F12" s="1">
+        <v>2.86</v>
+      </c>
+      <c r="G12" s="1">
+        <v>8</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1">
+        <v>117</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="1">
+        <v>761</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="G13" s="1">
+        <v>11</v>
+      </c>
+      <c r="H13" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1">
+        <v>80</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1195</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G14" s="1">
+        <v>8</v>
+      </c>
+      <c r="H14" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="1">
+        <v>111</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="1">
+        <v>2837</v>
+      </c>
+      <c r="F15" s="1">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="G15" s="1">
+        <v>6</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="1">
+        <v>93</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="1">
+        <v>3060</v>
+      </c>
+      <c r="F16" s="1">
+        <v>5.95</v>
+      </c>
+      <c r="G16" s="1">
+        <v>6</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="1">
+        <v>125</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="1">
+        <v>4015</v>
+      </c>
+      <c r="F17" s="1">
+        <v>2.88</v>
+      </c>
+      <c r="G17" s="1">
+        <v>5</v>
+      </c>
+      <c r="H17" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="1">
+        <v>1241</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="1">
+        <v>7515</v>
+      </c>
+      <c r="F18" s="1">
+        <v>18.46</v>
+      </c>
+      <c r="G18" s="1">
+        <v>3</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="1">
         <v>328</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="1">
+      <c r="B19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="1">
         <v>21436</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F19" s="1">
         <v>1.5</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G19" s="1">
         <v>1</v>
       </c>
-      <c r="H9" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H10" s="1"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H11" s="1"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H12" s="1"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H13" s="1"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H14" s="1"/>
+      <c r="H19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="H23" s="1"/>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="H24" s="1"/>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="H25" s="1"/>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="H26" s="1"/>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="H27" s="1"/>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="H28" s="1"/>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="H29" s="1"/>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="H30" s="1"/>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="H31" s="1"/>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="H32" s="1"/>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="H33" s="1"/>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="H35" s="1"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="H36" s="1"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="H37" s="1"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="H38" s="1"/>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="H39" s="1"/>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="H40" s="1"/>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="H41" s="1"/>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="H42" s="1"/>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="H43" s="1"/>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="H44" s="1"/>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="H45" s="1"/>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="H46" s="1"/>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="H47" s="1"/>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="H48" s="1"/>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="H49" s="1"/>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="H50" s="1"/>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="H51" s="1"/>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="H52" s="1"/>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="H53" s="1"/>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="H54" s="1"/>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="H55" s="1"/>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="H56" s="1"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="H57" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
